--- a/lai/valuationquan/AILOF/csiAILOFmodel1meancn.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel1meancn.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="32">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -107,14 +107,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>人工智能产业LOF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>买卖金额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>MAX</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -137,14 +129,6 @@
   <si>
     <t>单位：元</t>
     <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>人工智能产业LOF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>买卖金额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>最高价</t>
@@ -717,7 +701,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1029,6 +1013,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1038,7 +1025,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -1350,6 +1337,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>208000</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>210000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1392,7 +1382,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1704,6 +1694,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1713,7 +1706,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2025,6 +2018,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>388822.75954229012</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>416560.05776522681</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2067,7 +2063,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2379,6 +2375,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2388,7 +2387,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2700,6 +2699,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>180822.75954229012</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>206560.05776522681</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2721,11 +2723,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="432435200"/>
-        <c:axId val="432437120"/>
+        <c:axId val="621255680"/>
+        <c:axId val="621307008"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="432435200"/>
+        <c:axId val="621255680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2765,14 +2767,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="432437120"/>
+        <c:crossAx val="621307008"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="432437120"/>
+        <c:axId val="621307008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2821,7 +2823,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="432435200"/>
+        <c:crossAx val="621255680"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2951,7 +2953,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3263,6 +3265,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3272,7 +3277,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3584,6 +3589,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>208000</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>210000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3617,7 +3625,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3929,6 +3937,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3938,7 +3949,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4250,6 +4261,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>388822.75954229012</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>416560.05776522681</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4283,7 +4297,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4595,6 +4609,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4604,7 +4621,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4916,6 +4933,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>180822.75954229012</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>206560.05776522681</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4937,11 +4957,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="505470976"/>
-        <c:axId val="505473280"/>
+        <c:axId val="621360640"/>
+        <c:axId val="621362560"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="505470976"/>
+        <c:axId val="621360640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4951,14 +4971,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="505473280"/>
+        <c:crossAx val="621362560"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="505473280"/>
+        <c:axId val="621362560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4969,7 +4989,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="505470976"/>
+        <c:crossAx val="621360640"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5091,7 +5111,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5403,6 +5423,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5412,7 +5435,7 @@
               <c:f>模型一计算RSI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5724,6 +5747,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>215000</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>217000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5766,7 +5792,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6078,6 +6104,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6087,7 +6116,7 @@
               <c:f>模型一计算RSI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6399,6 +6428,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>406964.33522915788</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>435902.47659264668</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6441,7 +6473,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6753,6 +6785,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6762,7 +6797,7 @@
               <c:f>模型一计算RSI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7074,6 +7109,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>191964.33522915788</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>218902.47659264668</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7095,11 +7133,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="507685504"/>
-        <c:axId val="569890304"/>
+        <c:axId val="691889280"/>
+        <c:axId val="691890816"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="507685504"/>
+        <c:axId val="691889280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7139,14 +7177,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="569890304"/>
+        <c:crossAx val="691890816"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="569890304"/>
+        <c:axId val="691890816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7195,7 +7233,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="507685504"/>
+        <c:crossAx val="691889280"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7325,7 +7363,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7637,6 +7675,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7646,7 +7687,7 @@
               <c:f>模型一计算RSI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7958,6 +7999,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>215000</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>217000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7991,7 +8035,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8303,6 +8347,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8312,7 +8359,7 @@
               <c:f>模型一计算RSI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8624,6 +8671,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>406964.33522915788</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>435902.47659264668</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8657,7 +8707,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8969,6 +9019,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8978,7 +9031,7 @@
               <c:f>模型一计算RSI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9290,6 +9343,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>191964.33522915788</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>218902.47659264668</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9311,11 +9367,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="600797952"/>
-        <c:axId val="600799488"/>
+        <c:axId val="691914240"/>
+        <c:axId val="691915776"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="600797952"/>
+        <c:axId val="691914240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9325,14 +9381,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="600799488"/>
+        <c:crossAx val="691915776"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="600799488"/>
+        <c:axId val="691915776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9343,7 +9399,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="600797952"/>
+        <c:crossAx val="691914240"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9465,7 +9521,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9777,6 +9833,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9786,7 +9845,7 @@
               <c:f>模型一计算KDJ!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -10098,6 +10157,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>215000</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>217000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10140,7 +10202,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10452,6 +10514,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10461,7 +10526,7 @@
               <c:f>模型一计算KDJ!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -10773,6 +10838,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>405615.31121444347</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>434464.15679335035</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10815,7 +10883,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11127,6 +11195,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11136,7 +11207,7 @@
               <c:f>模型一计算KDJ!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11448,6 +11519,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>190615.31121444347</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>217464.15679335035</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11469,11 +11543,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="601261568"/>
-        <c:axId val="601263104"/>
+        <c:axId val="692029696"/>
+        <c:axId val="692031488"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="601261568"/>
+        <c:axId val="692029696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11513,14 +11587,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="601263104"/>
+        <c:crossAx val="692031488"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="601263104"/>
+        <c:axId val="692031488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11569,7 +11643,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="601261568"/>
+        <c:crossAx val="692029696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11699,7 +11773,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12011,6 +12085,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12020,7 +12097,7 @@
               <c:f>模型一计算KDJ!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -12332,6 +12409,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>215000</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>217000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12365,7 +12445,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12677,6 +12757,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12686,7 +12769,7 @@
               <c:f>模型一计算KDJ!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -12998,6 +13081,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>405615.31121444347</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>434464.15679335035</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13031,7 +13117,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13343,6 +13429,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13352,7 +13441,7 @@
               <c:f>模型一计算KDJ!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13664,6 +13753,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>190615.31121444347</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>217464.15679335035</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13685,11 +13777,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="601278336"/>
-        <c:axId val="601279872"/>
+        <c:axId val="692058752"/>
+        <c:axId val="692060544"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="601278336"/>
+        <c:axId val="692058752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13699,14 +13791,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="601279872"/>
+        <c:crossAx val="692060544"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="601279872"/>
+        <c:axId val="692060544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13717,7 +13809,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="601278336"/>
+        <c:crossAx val="692058752"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14244,7 +14336,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB106"/>
+  <dimension ref="A1:AB107"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -18024,6 +18116,35 @@
         <v>180822.75954229012</v>
       </c>
     </row>
+    <row r="107" spans="1:9" ht="12.75">
+      <c r="A107" s="13">
+        <v>46022</v>
+      </c>
+      <c r="B107" s="18">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C107" s="14">
+        <v>2000</v>
+      </c>
+      <c r="D107" s="15">
+        <v>833.33330021964309</v>
+      </c>
+      <c r="E107" s="15">
+        <v>173566.6838385908</v>
+      </c>
+      <c r="F107" s="15">
+        <v>416560.05776522681</v>
+      </c>
+      <c r="G107" s="15">
+        <v>210000</v>
+      </c>
+      <c r="H107" s="15">
+        <v>416560.05776522681</v>
+      </c>
+      <c r="I107" s="15">
+        <v>206560.05776522681</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18035,7 +18156,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH106"/>
+  <dimension ref="A1:AH107"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -18067,10 +18188,10 @@
         <v>17</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>3</v>
@@ -18091,19 +18212,19 @@
         <v>8</v>
       </c>
       <c r="J1" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="20" t="s">
+      <c r="M1" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="20" t="s">
+      <c r="N1" s="20" t="s">
         <v>22</v>
-      </c>
-      <c r="M1" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="N1" s="20" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1">
@@ -18113,7 +18234,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -23440,6 +23561,50 @@
       </c>
       <c r="N106" s="21">
         <v>63.365781700810651</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" ht="12.75">
+      <c r="A107" s="13">
+        <v>46022</v>
+      </c>
+      <c r="B107" s="18">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C107" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D107" s="15">
+        <v>833.33330021964309</v>
+      </c>
+      <c r="E107" s="15">
+        <v>181626.02469643299</v>
+      </c>
+      <c r="F107" s="15">
+        <v>435902.47659264668</v>
+      </c>
+      <c r="G107" s="15">
+        <v>217000</v>
+      </c>
+      <c r="H107" s="15">
+        <v>435902.47659264668</v>
+      </c>
+      <c r="I107" s="15">
+        <v>218902.47659264668</v>
+      </c>
+      <c r="J107" s="21">
+        <v>0.14900016784667969</v>
+      </c>
+      <c r="K107" s="21">
+        <v>0.14010746704699642</v>
+      </c>
+      <c r="L107" s="21">
+        <v>0.14900016784667969</v>
+      </c>
+      <c r="M107" s="23">
+        <v>0.20675190258530632</v>
+      </c>
+      <c r="N107" s="21">
+        <v>67.765986815617211</v>
       </c>
     </row>
   </sheetData>
@@ -23453,7 +23618,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AH106"/>
+  <dimension ref="A1:AH107"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -23482,13 +23647,13 @@
   <sheetData>
     <row r="1" spans="1:34" s="1" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>3</v>
@@ -23509,28 +23674,28 @@
         <v>8</v>
       </c>
       <c r="J1" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="O1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="P1" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="Q1" s="20" t="s">
         <v>31</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="O1" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="P1" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q1" s="20" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1">
@@ -23540,7 +23705,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -29683,6 +29848,59 @@
         <v>64.562273357270726</v>
       </c>
     </row>
+    <row r="107" spans="1:17" ht="12.75">
+      <c r="A107" s="13">
+        <v>46022</v>
+      </c>
+      <c r="B107" s="18">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C107" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D107" s="15">
+        <v>833.33330021964309</v>
+      </c>
+      <c r="E107" s="15">
+        <v>181026.72480387357</v>
+      </c>
+      <c r="F107" s="15">
+        <v>434464.15679335035</v>
+      </c>
+      <c r="G107" s="15">
+        <v>217000</v>
+      </c>
+      <c r="H107" s="15">
+        <v>434464.15679335035</v>
+      </c>
+      <c r="I107" s="15">
+        <v>217464.15679335035</v>
+      </c>
+      <c r="J107" s="15">
+        <v>2.4330000877380371</v>
+      </c>
+      <c r="K107" s="15">
+        <v>2.2260000705718994</v>
+      </c>
+      <c r="L107" s="19">
+        <v>2.8289999961853027</v>
+      </c>
+      <c r="M107" s="19">
+        <v>1.2999999523162842</v>
+      </c>
+      <c r="N107" s="21">
+        <v>71.942453334905125</v>
+      </c>
+      <c r="O107" s="21">
+        <v>70.756255946162113</v>
+      </c>
+      <c r="P107" s="21">
+        <v>72.227818114754385</v>
+      </c>
+      <c r="Q107" s="21">
+        <v>67.813131608977557</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/lai/valuationquan/AILOF/csiAILOFmodel1meancn.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel1meancn.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="30">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -103,10 +103,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>MAX</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -125,10 +121,6 @@
   <si>
     <t>RSI</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单位：元</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>最高价</t>
@@ -701,7 +693,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1016,6 +1008,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1025,7 +1020,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -1340,6 +1335,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>210000</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>212000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1382,7 +1380,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1697,6 +1695,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1706,7 +1707,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2021,6 +2022,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>416560.05776522681</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>453620.51101696113</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2063,7 +2067,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2378,6 +2382,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2387,7 +2394,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2702,6 +2709,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>206560.05776522681</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>241620.51101696113</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2723,11 +2733,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="621255680"/>
-        <c:axId val="621307008"/>
+        <c:axId val="576518016"/>
+        <c:axId val="576524288"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="621255680"/>
+        <c:axId val="576518016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2767,14 +2777,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="621307008"/>
+        <c:crossAx val="576524288"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="621307008"/>
+        <c:axId val="576524288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2823,7 +2833,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="621255680"/>
+        <c:crossAx val="576518016"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2953,7 +2963,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3268,6 +3278,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3277,7 +3290,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3592,6 +3605,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>210000</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>212000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3625,7 +3641,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3940,6 +3956,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3949,7 +3968,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4264,6 +4283,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>416560.05776522681</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>453620.51101696113</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4297,7 +4319,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4612,6 +4634,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4621,7 +4646,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4936,6 +4961,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>206560.05776522681</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>241620.51101696113</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4957,11 +4985,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="621360640"/>
-        <c:axId val="621362560"/>
+        <c:axId val="581240320"/>
+        <c:axId val="581255552"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="621360640"/>
+        <c:axId val="581240320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4971,14 +4999,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="621362560"/>
+        <c:crossAx val="581255552"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="621362560"/>
+        <c:axId val="581255552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4989,7 +5017,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="621360640"/>
+        <c:crossAx val="581240320"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5111,7 +5139,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5426,6 +5454,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5435,7 +5466,7 @@
               <c:f>模型一计算RSI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5750,6 +5781,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>217000</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>219000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5792,7 +5826,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6107,6 +6141,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6116,7 +6153,7 @@
               <c:f>模型一计算RSI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6431,6 +6468,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>435902.47659264668</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>474590.91591369454</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6473,7 +6513,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6788,6 +6828,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6797,7 +6840,7 @@
               <c:f>模型一计算RSI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7112,6 +7155,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>218902.47659264668</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>255590.91591369454</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7133,11 +7179,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="691889280"/>
-        <c:axId val="691890816"/>
+        <c:axId val="581276800"/>
+        <c:axId val="581278720"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="691889280"/>
+        <c:axId val="581276800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7177,14 +7223,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="691890816"/>
+        <c:crossAx val="581278720"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="691890816"/>
+        <c:axId val="581278720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7233,7 +7279,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="691889280"/>
+        <c:crossAx val="581276800"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7363,7 +7409,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7678,6 +7724,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7687,7 +7736,7 @@
               <c:f>模型一计算RSI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8002,6 +8051,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>217000</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>219000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8035,7 +8087,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8350,6 +8402,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8359,7 +8414,7 @@
               <c:f>模型一计算RSI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8674,6 +8729,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>435902.47659264668</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>474590.91591369454</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8707,7 +8765,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9022,6 +9080,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9031,7 +9092,7 @@
               <c:f>模型一计算RSI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9346,6 +9407,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>218902.47659264668</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>255590.91591369454</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9367,11 +9431,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="691914240"/>
-        <c:axId val="691915776"/>
+        <c:axId val="635633664"/>
+        <c:axId val="635635200"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="691914240"/>
+        <c:axId val="635633664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9381,14 +9445,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="691915776"/>
+        <c:crossAx val="635635200"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="691915776"/>
+        <c:axId val="635635200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9399,7 +9463,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="691914240"/>
+        <c:crossAx val="635633664"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9521,7 +9585,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9836,6 +9900,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9845,7 +9912,7 @@
               <c:f>模型一计算KDJ!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -10160,6 +10227,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>217000</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>219000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10202,7 +10272,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10517,6 +10587,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10526,7 +10599,7 @@
               <c:f>模型一计算KDJ!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -10841,6 +10914,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>434464.15679335035</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>473031.53759439802</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10883,7 +10959,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11198,6 +11274,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11207,7 +11286,7 @@
               <c:f>模型一计算KDJ!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11522,6 +11601,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>217464.15679335035</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>254031.53759439802</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11543,11 +11625,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="692029696"/>
-        <c:axId val="692031488"/>
+        <c:axId val="635671296"/>
+        <c:axId val="635672832"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="692029696"/>
+        <c:axId val="635671296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11587,14 +11669,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="692031488"/>
+        <c:crossAx val="635672832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="692031488"/>
+        <c:axId val="635672832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11643,7 +11725,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="692029696"/>
+        <c:crossAx val="635671296"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11773,7 +11855,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12088,6 +12170,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12097,7 +12182,7 @@
               <c:f>模型一计算KDJ!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -12412,6 +12497,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>217000</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>219000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12445,7 +12533,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12760,6 +12848,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12769,7 +12860,7 @@
               <c:f>模型一计算KDJ!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -13084,6 +13175,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>434464.15679335035</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>473031.53759439802</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13117,7 +13211,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13432,6 +13526,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13441,7 +13538,7 @@
               <c:f>模型一计算KDJ!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13756,6 +13853,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>217464.15679335035</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>254031.53759439802</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13777,11 +13877,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="692058752"/>
-        <c:axId val="692060544"/>
+        <c:axId val="636028032"/>
+        <c:axId val="636029568"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="692058752"/>
+        <c:axId val="636028032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13791,14 +13891,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="692060544"/>
+        <c:crossAx val="636029568"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="692060544"/>
+        <c:axId val="636029568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13809,7 +13909,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="692058752"/>
+        <c:crossAx val="636028032"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13851,7 +13951,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13889,7 +13989,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13930,7 +14030,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13968,7 +14068,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14011,7 +14111,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14049,7 +14149,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14327,7 +14427,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -14336,7 +14436,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB107"/>
+  <dimension ref="A1:AB108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -18145,6 +18245,35 @@
         <v>206560.05776522681</v>
       </c>
     </row>
+    <row r="108" spans="1:9" ht="12.75">
+      <c r="A108" s="13">
+        <v>46052</v>
+      </c>
+      <c r="B108" s="18">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C108" s="14">
+        <v>2000</v>
+      </c>
+      <c r="D108" s="15">
+        <v>768.63950863415198</v>
+      </c>
+      <c r="E108" s="15">
+        <v>174335.32334722497</v>
+      </c>
+      <c r="F108" s="15">
+        <v>453620.51101696113</v>
+      </c>
+      <c r="G108" s="15">
+        <v>212000</v>
+      </c>
+      <c r="H108" s="15">
+        <v>453620.51101696113</v>
+      </c>
+      <c r="I108" s="15">
+        <v>241620.51101696113</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18156,7 +18285,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH107"/>
+  <dimension ref="A1:AH108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -18185,7 +18314,7 @@
   <sheetData>
     <row r="1" spans="1:34" s="1" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>1</v>
@@ -18212,19 +18341,19 @@
         <v>8</v>
       </c>
       <c r="J1" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="20" t="s">
+      <c r="L1" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="20" t="s">
+      <c r="M1" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="N1" s="20" t="s">
         <v>21</v>
-      </c>
-      <c r="N1" s="20" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1">
@@ -18234,7 +18363,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -23605,6 +23734,50 @@
       </c>
       <c r="N107" s="21">
         <v>67.765986815617211</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" ht="12.75">
+      <c r="A108" s="13">
+        <v>46052</v>
+      </c>
+      <c r="B108" s="18">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C108" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D108" s="15">
+        <v>768.63950863415198</v>
+      </c>
+      <c r="E108" s="15">
+        <v>182394.66420506715</v>
+      </c>
+      <c r="F108" s="15">
+        <v>474590.91591369454</v>
+      </c>
+      <c r="G108" s="15">
+        <v>219000</v>
+      </c>
+      <c r="H108" s="15">
+        <v>474590.91591369454</v>
+      </c>
+      <c r="I108" s="15">
+        <v>255590.91591369454</v>
+      </c>
+      <c r="J108" s="21">
+        <v>0.20199990272521973</v>
+      </c>
+      <c r="K108" s="21">
+        <v>0.15042287299336696</v>
+      </c>
+      <c r="L108" s="21">
+        <v>0.20199990272521973</v>
+      </c>
+      <c r="M108" s="23">
+        <v>0.20595990260862521</v>
+      </c>
+      <c r="N108" s="21">
+        <v>73.035028220618088</v>
       </c>
     </row>
   </sheetData>
@@ -23618,7 +23791,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AH107"/>
+  <dimension ref="A1:AH108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -23674,28 +23847,28 @@
         <v>8</v>
       </c>
       <c r="J1" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="O1" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="P1" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="O1" s="20" t="s">
+      <c r="Q1" s="20" t="s">
         <v>29</v>
-      </c>
-      <c r="P1" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q1" s="20" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1">
@@ -23705,7 +23878,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -29901,6 +30074,59 @@
         <v>67.813131608977557</v>
       </c>
     </row>
+    <row r="108" spans="1:17" ht="12.75">
+      <c r="A108" s="13">
+        <v>46052</v>
+      </c>
+      <c r="B108" s="18">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C108" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D108" s="15">
+        <v>768.63950863415198</v>
+      </c>
+      <c r="E108" s="15">
+        <v>181795.36431250774</v>
+      </c>
+      <c r="F108" s="15">
+        <v>473031.53759439802</v>
+      </c>
+      <c r="G108" s="15">
+        <v>219000</v>
+      </c>
+      <c r="H108" s="15">
+        <v>473031.53759439802</v>
+      </c>
+      <c r="I108" s="15">
+        <v>254031.53759439802</v>
+      </c>
+      <c r="J108" s="15">
+        <v>2.684999942779541</v>
+      </c>
+      <c r="K108" s="15">
+        <v>2.4119999408721924</v>
+      </c>
+      <c r="L108" s="19">
+        <v>2.8289999961853027</v>
+      </c>
+      <c r="M108" s="19">
+        <v>1.4229999780654907</v>
+      </c>
+      <c r="N108" s="21">
+        <v>83.854907882845595</v>
+      </c>
+      <c r="O108" s="21">
+        <v>75.122473258389945</v>
+      </c>
+      <c r="P108" s="21">
+        <v>73.192703162632895</v>
+      </c>
+      <c r="Q108" s="21">
+        <v>78.982013449904031</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/lai/valuationquan/AILOF/csiAILOFmodel1meancn.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel1meancn.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="31">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -121,6 +121,10 @@
   <si>
     <t>RSI</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单位：元</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>最高价</t>
@@ -693,7 +697,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1011,6 +1015,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1020,7 +1027,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -1338,6 +1345,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>212000</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>214000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1380,7 +1390,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1698,6 +1708,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1707,7 +1720,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2025,6 +2038,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>453620.51101696113</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>442022.34382522095</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2067,7 +2083,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2385,6 +2401,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2394,7 +2413,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2712,6 +2731,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>241620.51101696113</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>228022.34382522095</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2733,11 +2755,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="576518016"/>
-        <c:axId val="576524288"/>
+        <c:axId val="446822272"/>
+        <c:axId val="483329920"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="576518016"/>
+        <c:axId val="446822272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2777,14 +2799,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="576524288"/>
+        <c:crossAx val="483329920"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="576524288"/>
+        <c:axId val="483329920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2833,7 +2855,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="576518016"/>
+        <c:crossAx val="446822272"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2963,7 +2985,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3281,6 +3303,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3290,7 +3315,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3608,6 +3633,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>212000</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>214000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3641,7 +3669,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3959,6 +3987,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3968,7 +3999,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4286,6 +4317,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>453620.51101696113</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>442022.34382522095</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4319,7 +4353,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4637,6 +4671,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4646,7 +4683,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4964,6 +5001,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>241620.51101696113</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>228022.34382522095</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4985,11 +5025,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="581240320"/>
-        <c:axId val="581255552"/>
+        <c:axId val="497369472"/>
+        <c:axId val="497371776"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="581240320"/>
+        <c:axId val="497369472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4999,14 +5039,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="581255552"/>
+        <c:crossAx val="497371776"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="581255552"/>
+        <c:axId val="497371776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5017,7 +5057,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="581240320"/>
+        <c:crossAx val="497369472"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5139,7 +5179,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5457,6 +5497,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5466,7 +5509,7 @@
               <c:f>模型一计算RSI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5784,6 +5827,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>219000</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>221000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5826,7 +5872,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6144,6 +6190,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6153,7 +6202,7 @@
               <c:f>模型一计算RSI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6471,6 +6520,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>474590.91591369454</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>462364.11958165164</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6513,7 +6565,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6831,6 +6883,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6840,7 +6895,7 @@
               <c:f>模型一计算RSI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7158,6 +7213,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>255590.91591369454</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>241364.11958165164</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7179,11 +7237,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="581276800"/>
-        <c:axId val="581278720"/>
+        <c:axId val="531904384"/>
+        <c:axId val="533180416"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="581276800"/>
+        <c:axId val="531904384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7223,14 +7281,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="581278720"/>
+        <c:crossAx val="533180416"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="581278720"/>
+        <c:axId val="533180416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7279,7 +7337,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="581276800"/>
+        <c:crossAx val="531904384"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7409,7 +7467,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7727,6 +7785,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7736,7 +7797,7 @@
               <c:f>模型一计算RSI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8054,6 +8115,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>219000</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>221000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8087,7 +8151,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8405,6 +8469,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8414,7 +8481,7 @@
               <c:f>模型一计算RSI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8732,6 +8799,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>474590.91591369454</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>462364.11958165164</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8765,7 +8835,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9083,6 +9153,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9092,7 +9165,7 @@
               <c:f>模型一计算RSI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9410,6 +9483,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>255590.91591369454</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>241364.11958165164</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9431,11 +9507,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="635633664"/>
-        <c:axId val="635635200"/>
+        <c:axId val="691714688"/>
+        <c:axId val="528298752"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="635633664"/>
+        <c:axId val="691714688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9445,14 +9521,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="635635200"/>
+        <c:crossAx val="528298752"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="635635200"/>
+        <c:axId val="528298752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9463,7 +9539,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="635633664"/>
+        <c:crossAx val="691714688"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9585,7 +9661,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9903,6 +9979,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9912,7 +9991,7 @@
               <c:f>模型一计算KDJ!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -10230,6 +10309,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>219000</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>221000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10272,7 +10354,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10590,6 +10672,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10599,7 +10684,7 @@
               <c:f>模型一计算KDJ!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -10917,6 +11002,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>473031.53759439802</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>460851.48669512541</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10959,7 +11047,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11277,6 +11365,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11286,7 +11377,7 @@
               <c:f>模型一计算KDJ!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11604,6 +11695,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>254031.53759439802</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>239851.48669512541</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11625,11 +11719,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="635671296"/>
-        <c:axId val="635672832"/>
+        <c:axId val="528318464"/>
+        <c:axId val="528320000"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="635671296"/>
+        <c:axId val="528318464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11669,14 +11763,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="635672832"/>
+        <c:crossAx val="528320000"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="635672832"/>
+        <c:axId val="528320000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11725,7 +11819,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="635671296"/>
+        <c:crossAx val="528318464"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11855,7 +11949,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12173,6 +12267,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12182,7 +12279,7 @@
               <c:f>模型一计算KDJ!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -12500,6 +12597,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>219000</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>221000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12533,7 +12633,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12851,6 +12951,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12860,7 +12963,7 @@
               <c:f>模型一计算KDJ!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -13178,6 +13281,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>473031.53759439802</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>460851.48669512541</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13211,7 +13317,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13529,6 +13635,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13538,7 +13647,7 @@
               <c:f>模型一计算KDJ!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13856,6 +13965,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>254031.53759439802</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>239851.48669512541</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13877,11 +13989,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="636028032"/>
-        <c:axId val="636029568"/>
+        <c:axId val="528347520"/>
+        <c:axId val="528349056"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="636028032"/>
+        <c:axId val="528347520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13891,14 +14003,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="636029568"/>
+        <c:crossAx val="528349056"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="636029568"/>
+        <c:axId val="528349056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13909,7 +14021,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="636028032"/>
+        <c:crossAx val="528347520"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13951,7 +14063,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13989,7 +14101,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14030,7 +14142,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14068,7 +14180,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14111,7 +14223,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14149,7 +14261,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14427,7 +14539,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -14436,7 +14548,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB108"/>
+  <dimension ref="A1:AB109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -18274,6 +18386,35 @@
         <v>241620.51101696113</v>
       </c>
     </row>
+    <row r="109" spans="1:9" ht="12.75">
+      <c r="A109" s="13">
+        <v>46080</v>
+      </c>
+      <c r="B109" s="18">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C109" s="14">
+        <v>2000</v>
+      </c>
+      <c r="D109" s="15">
+        <v>792.39304909694238</v>
+      </c>
+      <c r="E109" s="15">
+        <v>175127.71639632192</v>
+      </c>
+      <c r="F109" s="15">
+        <v>442022.34382522095</v>
+      </c>
+      <c r="G109" s="15">
+        <v>214000</v>
+      </c>
+      <c r="H109" s="15">
+        <v>442022.34382522095</v>
+      </c>
+      <c r="I109" s="15">
+        <v>228022.34382522095</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18285,7 +18426,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH108"/>
+  <dimension ref="A1:AH109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -18363,7 +18504,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -23778,6 +23919,50 @@
       </c>
       <c r="N108" s="21">
         <v>73.035028220618088</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" ht="12.75">
+      <c r="A109" s="13">
+        <v>46080</v>
+      </c>
+      <c r="B109" s="18">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C109" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D109" s="15">
+        <v>792.39304909694238</v>
+      </c>
+      <c r="E109" s="15">
+        <v>183187.0572541641</v>
+      </c>
+      <c r="F109" s="15">
+        <v>462364.11958165164</v>
+      </c>
+      <c r="G109" s="15">
+        <v>221000</v>
+      </c>
+      <c r="H109" s="15">
+        <v>462364.11958165164</v>
+      </c>
+      <c r="I109" s="15">
+        <v>241364.11958165164</v>
+      </c>
+      <c r="J109" s="21">
+        <v>0</v>
+      </c>
+      <c r="K109" s="21">
+        <v>0.12535239416113914</v>
+      </c>
+      <c r="L109" s="21">
+        <v>7.8000068664550781E-2</v>
+      </c>
+      <c r="M109" s="23">
+        <v>0.18463326361794616</v>
+      </c>
+      <c r="N109" s="21">
+        <v>67.892638468724456</v>
       </c>
     </row>
   </sheetData>
@@ -23791,7 +23976,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AH108"/>
+  <dimension ref="A1:AH109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -23847,28 +24032,28 @@
         <v>8</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O1" s="20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P1" s="20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q1" s="20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1">
@@ -30127,6 +30312,59 @@
         <v>78.982013449904031</v>
       </c>
     </row>
+    <row r="109" spans="1:17" ht="12.75">
+      <c r="A109" s="13">
+        <v>46080</v>
+      </c>
+      <c r="B109" s="18">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C109" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D109" s="15">
+        <v>792.39304909694238</v>
+      </c>
+      <c r="E109" s="15">
+        <v>182587.75736160469</v>
+      </c>
+      <c r="F109" s="15">
+        <v>460851.48669512541</v>
+      </c>
+      <c r="G109" s="15">
+        <v>221000</v>
+      </c>
+      <c r="H109" s="15">
+        <v>460851.48669512541</v>
+      </c>
+      <c r="I109" s="15">
+        <v>239851.48669512541</v>
+      </c>
+      <c r="J109" s="15">
+        <v>2.6319999694824219</v>
+      </c>
+      <c r="K109" s="15">
+        <v>2.3610000610351562</v>
+      </c>
+      <c r="L109" s="19">
+        <v>2.8289999961853027</v>
+      </c>
+      <c r="M109" s="19">
+        <v>1.4299999475479126</v>
+      </c>
+      <c r="N109" s="21">
+        <v>78.198709352850372</v>
+      </c>
+      <c r="O109" s="21">
+        <v>76.147885289876754</v>
+      </c>
+      <c r="P109" s="21">
+        <v>74.177763871714191</v>
+      </c>
+      <c r="Q109" s="21">
+        <v>80.088128126201894</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/lai/valuationquan/AILOF/csiAILOFmodel1meancn.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel1meancn.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="34">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -127,6 +127,14 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工智能产业LOF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>最高价</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -157,6 +165,10 @@
   <si>
     <t>J</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>单位：元</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -697,7 +709,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1018,6 +1030,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1027,7 +1042,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -1348,6 +1363,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>214000</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>216000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1390,7 +1408,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1711,6 +1729,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1720,7 +1741,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2041,6 +2062,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>442022.34382522095</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>399014.52605583996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2083,7 +2107,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2404,6 +2428,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2413,7 +2440,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2734,6 +2761,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>228022.34382522095</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>183014.52605583996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2755,11 +2785,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="446822272"/>
-        <c:axId val="483329920"/>
+        <c:axId val="493783680"/>
+        <c:axId val="493822336"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="446822272"/>
+        <c:axId val="493783680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2799,14 +2829,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="483329920"/>
+        <c:crossAx val="493822336"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="483329920"/>
+        <c:axId val="493822336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2855,7 +2885,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="446822272"/>
+        <c:crossAx val="493783680"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2985,7 +3015,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3306,6 +3336,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3315,7 +3348,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3636,6 +3669,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>214000</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>216000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3669,7 +3705,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3990,6 +4026,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3999,7 +4038,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4320,6 +4359,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>442022.34382522095</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>399014.52605583996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4353,7 +4395,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4674,6 +4716,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4683,7 +4728,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5004,6 +5049,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>228022.34382522095</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>183014.52605583996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5025,11 +5073,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="497369472"/>
-        <c:axId val="497371776"/>
+        <c:axId val="377137408"/>
+        <c:axId val="377139200"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="497369472"/>
+        <c:axId val="377137408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5039,14 +5087,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="497371776"/>
+        <c:crossAx val="377139200"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="497371776"/>
+        <c:axId val="377139200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5057,7 +5105,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="497369472"/>
+        <c:crossAx val="377137408"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5179,7 +5227,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5500,6 +5548,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5509,7 +5560,7 @@
               <c:f>模型一计算RSI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5830,6 +5881,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>221000</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>223000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5872,7 +5926,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6193,6 +6247,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6202,7 +6259,7 @@
               <c:f>模型一计算RSI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6523,6 +6580,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>462364.11958165164</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>417285.05145775672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6565,7 +6625,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6886,6 +6946,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6895,7 +6958,7 @@
               <c:f>模型一计算RSI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7216,6 +7279,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>241364.11958165164</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>194285.05145775672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7237,11 +7303,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="531904384"/>
-        <c:axId val="533180416"/>
+        <c:axId val="363736064"/>
+        <c:axId val="363741952"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="531904384"/>
+        <c:axId val="363736064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7281,14 +7347,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="533180416"/>
+        <c:crossAx val="363741952"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="533180416"/>
+        <c:axId val="363741952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7337,7 +7403,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="531904384"/>
+        <c:crossAx val="363736064"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7467,7 +7533,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7788,6 +7854,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7797,7 +7866,7 @@
               <c:f>模型一计算RSI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8118,6 +8187,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>221000</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>223000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8151,7 +8223,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8472,6 +8544,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8481,7 +8556,7 @@
               <c:f>模型一计算RSI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8802,6 +8877,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>462364.11958165164</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>417285.05145775672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8835,7 +8913,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9156,6 +9234,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9165,7 +9246,7 @@
               <c:f>模型一计算RSI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9486,6 +9567,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>241364.11958165164</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>194285.05145775672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9507,11 +9591,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="691714688"/>
-        <c:axId val="528298752"/>
+        <c:axId val="363761024"/>
+        <c:axId val="363762816"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="691714688"/>
+        <c:axId val="363761024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9521,14 +9605,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="528298752"/>
+        <c:crossAx val="363762816"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="528298752"/>
+        <c:axId val="363762816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9539,7 +9623,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="691714688"/>
+        <c:crossAx val="363761024"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9661,7 +9745,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9982,6 +10066,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9991,7 +10078,7 @@
               <c:f>模型一计算KDJ!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -10312,6 +10399,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>221000</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>223000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10354,7 +10444,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10675,6 +10765,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10684,7 +10777,7 @@
               <c:f>模型一计算KDJ!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -11005,6 +11098,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>460851.48669512541</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>415926.43862532912</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11047,7 +11143,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11368,6 +11464,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11377,7 +11476,7 @@
               <c:f>模型一计算KDJ!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11698,6 +11797,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>239851.48669512541</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>192926.43862532912</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11719,11 +11821,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="528318464"/>
-        <c:axId val="528320000"/>
+        <c:axId val="390250880"/>
+        <c:axId val="390252416"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="528318464"/>
+        <c:axId val="390250880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11763,14 +11865,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528320000"/>
+        <c:crossAx val="390252416"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="528320000"/>
+        <c:axId val="390252416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11819,7 +11921,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528318464"/>
+        <c:crossAx val="390250880"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11949,7 +12051,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12270,6 +12372,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12279,7 +12384,7 @@
               <c:f>模型一计算KDJ!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -12600,6 +12705,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>221000</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>223000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12633,7 +12741,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12954,6 +13062,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12963,7 +13074,7 @@
               <c:f>模型一计算KDJ!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -13284,6 +13395,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>460851.48669512541</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>415926.43862532912</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13317,7 +13431,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13638,6 +13752,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13647,7 +13764,7 @@
               <c:f>模型一计算KDJ!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13968,6 +14085,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>239851.48669512541</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>192926.43862532912</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13989,11 +14109,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="528347520"/>
-        <c:axId val="528349056"/>
+        <c:axId val="389952256"/>
+        <c:axId val="389953792"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="528347520"/>
+        <c:axId val="389952256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14003,14 +14123,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="528349056"/>
+        <c:crossAx val="389953792"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="528349056"/>
+        <c:axId val="389953792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14021,7 +14141,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="528347520"/>
+        <c:crossAx val="389952256"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14063,7 +14183,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14101,7 +14221,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14142,7 +14262,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14180,7 +14300,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14223,7 +14343,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14261,7 +14381,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14539,7 +14659,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -14548,7 +14668,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB109"/>
+  <dimension ref="A1:AB110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -18415,6 +18535,35 @@
         <v>228022.34382522095</v>
       </c>
     </row>
+    <row r="110" spans="1:9" ht="12.75">
+      <c r="A110" s="13">
+        <v>46112</v>
+      </c>
+      <c r="B110" s="18">
+        <v>2.2669999599456787</v>
+      </c>
+      <c r="C110" s="14">
+        <v>2000</v>
+      </c>
+      <c r="D110" s="15">
+        <v>882.22321805772049</v>
+      </c>
+      <c r="E110" s="15">
+        <v>176009.93961437963</v>
+      </c>
+      <c r="F110" s="15">
+        <v>399014.52605583996</v>
+      </c>
+      <c r="G110" s="15">
+        <v>216000</v>
+      </c>
+      <c r="H110" s="15">
+        <v>399014.52605583996</v>
+      </c>
+      <c r="I110" s="15">
+        <v>183014.52605583996</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18426,7 +18575,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH109"/>
+  <dimension ref="A1:AH110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -23965,6 +24114,50 @@
         <v>67.892638468724456</v>
       </c>
     </row>
+    <row r="110" spans="1:14" ht="12.75">
+      <c r="A110" s="13">
+        <v>46112</v>
+      </c>
+      <c r="B110" s="18">
+        <v>2.2669999599456787</v>
+      </c>
+      <c r="C110" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D110" s="15">
+        <v>882.22321805772049</v>
+      </c>
+      <c r="E110" s="15">
+        <v>184069.28047222181</v>
+      </c>
+      <c r="F110" s="15">
+        <v>417285.05145775672</v>
+      </c>
+      <c r="G110" s="15">
+        <v>223000</v>
+      </c>
+      <c r="H110" s="15">
+        <v>417285.05145775672</v>
+      </c>
+      <c r="I110" s="15">
+        <v>194285.05145775672</v>
+      </c>
+      <c r="J110" s="21">
+        <v>0</v>
+      </c>
+      <c r="K110" s="21">
+        <v>0.10446032846761595</v>
+      </c>
+      <c r="L110" s="21">
+        <v>0.25699996948242188</v>
+      </c>
+      <c r="M110" s="23">
+        <v>0.19669438126202543</v>
+      </c>
+      <c r="N110" s="21">
+        <v>53.107937195450262</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23976,7 +24169,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AH109"/>
+  <dimension ref="A1:AH110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -24005,10 +24198,10 @@
   <sheetData>
     <row r="1" spans="1:34" s="1" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>2</v>
@@ -24032,28 +24225,28 @@
         <v>8</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="O1" s="20" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P1" s="20" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Q1" s="20" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1">
@@ -24063,7 +24256,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -30365,6 +30558,59 @@
         <v>80.088128126201894</v>
       </c>
     </row>
+    <row r="110" spans="1:17" ht="12.75">
+      <c r="A110" s="13">
+        <v>46112</v>
+      </c>
+      <c r="B110" s="18">
+        <v>2.2669999599456787</v>
+      </c>
+      <c r="C110" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D110" s="15">
+        <v>882.22321805772049</v>
+      </c>
+      <c r="E110" s="15">
+        <v>183469.9805796624</v>
+      </c>
+      <c r="F110" s="15">
+        <v>415926.43862532912</v>
+      </c>
+      <c r="G110" s="15">
+        <v>223000</v>
+      </c>
+      <c r="H110" s="15">
+        <v>415926.43862532912</v>
+      </c>
+      <c r="I110" s="15">
+        <v>192926.43862532912</v>
+      </c>
+      <c r="J110" s="15">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="K110" s="15">
+        <v>2.25</v>
+      </c>
+      <c r="L110" s="19">
+        <v>2.8289999961853027</v>
+      </c>
+      <c r="M110" s="19">
+        <v>1.4939999580383301</v>
+      </c>
+      <c r="N110" s="21">
+        <v>57.902620211179922</v>
+      </c>
+      <c r="O110" s="21">
+        <v>70.066130263644482</v>
+      </c>
+      <c r="P110" s="21">
+        <v>72.807219335690959</v>
+      </c>
+      <c r="Q110" s="21">
+        <v>64.583952119551526</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/lai/valuationquan/AILOF/csiAILOFmodel1meancn.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel1meancn.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="31">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -120,18 +120,6 @@
   </si>
   <si>
     <t>RSI</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单位：元</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>人工智能产业LOF</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -709,7 +697,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1033,6 +1021,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1042,7 +1033,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -1366,6 +1357,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>216000</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>218000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1408,7 +1402,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1732,6 +1726,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1741,7 +1738,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2065,6 +2062,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>399014.52605583996</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>493067.72480987286</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2107,7 +2107,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2431,6 +2431,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2440,7 +2443,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2764,6 +2767,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>183014.52605583996</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>275067.72480987286</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2785,11 +2791,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="493783680"/>
-        <c:axId val="493822336"/>
+        <c:axId val="514263296"/>
+        <c:axId val="525312768"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="493783680"/>
+        <c:axId val="514263296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2829,14 +2835,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="493822336"/>
+        <c:crossAx val="525312768"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="493822336"/>
+        <c:axId val="525312768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2885,7 +2891,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="493783680"/>
+        <c:crossAx val="514263296"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3015,7 +3021,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3339,6 +3345,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3348,7 +3357,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3672,6 +3681,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>216000</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>218000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3705,7 +3717,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4029,6 +4041,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4038,7 +4053,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4362,6 +4377,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>399014.52605583996</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>493067.72480987286</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4395,7 +4413,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4719,6 +4737,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4728,7 +4749,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5052,6 +5073,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>183014.52605583996</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>275067.72480987286</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5073,11 +5097,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="377137408"/>
-        <c:axId val="377139200"/>
+        <c:axId val="527323520"/>
+        <c:axId val="527325440"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="377137408"/>
+        <c:axId val="527323520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5087,14 +5111,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="377139200"/>
+        <c:crossAx val="527325440"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="377139200"/>
+        <c:axId val="527325440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5105,7 +5129,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="377137408"/>
+        <c:crossAx val="527323520"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5227,7 +5251,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5551,6 +5575,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5560,7 +5587,7 @@
               <c:f>模型一计算RSI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5884,6 +5911,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>223000</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>225000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5926,7 +5956,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6250,6 +6280,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6259,7 +6292,7 @@
               <c:f>模型一计算RSI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6583,6 +6616,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>417285.05145775672</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>515553.28549581306</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6625,7 +6661,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6949,6 +6985,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6958,7 +6997,7 @@
               <c:f>模型一计算RSI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7282,6 +7321,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>194285.05145775672</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>290553.28549581306</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7303,11 +7345,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="363736064"/>
-        <c:axId val="363741952"/>
+        <c:axId val="527359360"/>
+        <c:axId val="484852864"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="363736064"/>
+        <c:axId val="527359360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7347,14 +7389,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="363741952"/>
+        <c:crossAx val="484852864"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="363741952"/>
+        <c:axId val="484852864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7403,7 +7445,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="363736064"/>
+        <c:crossAx val="527359360"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7533,7 +7575,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7857,6 +7899,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7866,7 +7911,7 @@
               <c:f>模型一计算RSI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8190,6 +8235,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>223000</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>225000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8223,7 +8271,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8547,6 +8595,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8556,7 +8607,7 @@
               <c:f>模型一计算RSI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8880,6 +8931,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>417285.05145775672</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>515553.28549581306</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8913,7 +8967,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9237,6 +9291,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9246,7 +9303,7 @@
               <c:f>模型一计算RSI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9570,6 +9627,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>194285.05145775672</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>290553.28549581306</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9591,11 +9651,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="363761024"/>
-        <c:axId val="363762816"/>
+        <c:axId val="484868096"/>
+        <c:axId val="484869632"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="363761024"/>
+        <c:axId val="484868096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9605,14 +9665,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="363762816"/>
+        <c:crossAx val="484869632"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="363762816"/>
+        <c:axId val="484869632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9623,7 +9683,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="363761024"/>
+        <c:crossAx val="484868096"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9745,7 +9805,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10069,6 +10129,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10078,7 +10141,7 @@
               <c:f>模型一计算KDJ!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -10402,6 +10465,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>223000</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>225000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10444,7 +10510,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10768,6 +10834,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10777,7 +10846,7 @@
               <c:f>模型一计算KDJ!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -11101,6 +11170,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>415926.43862532912</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>513881.23881843378</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11143,7 +11215,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11467,6 +11539,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11476,7 +11551,7 @@
               <c:f>模型一计算KDJ!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11800,6 +11875,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>192926.43862532912</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>288881.23881843378</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11821,11 +11899,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="390250880"/>
-        <c:axId val="390252416"/>
+        <c:axId val="483480320"/>
+        <c:axId val="483481856"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="390250880"/>
+        <c:axId val="483480320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11865,14 +11943,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="390252416"/>
+        <c:crossAx val="483481856"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="390252416"/>
+        <c:axId val="483481856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11921,7 +11999,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="390250880"/>
+        <c:crossAx val="483480320"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12051,7 +12129,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12375,6 +12453,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12384,7 +12465,7 @@
               <c:f>模型一计算KDJ!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -12708,6 +12789,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>223000</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>225000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12741,7 +12825,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13065,6 +13149,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13074,7 +13161,7 @@
               <c:f>模型一计算KDJ!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -13398,6 +13485,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>415926.43862532912</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>513881.23881843378</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13431,7 +13521,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13755,6 +13845,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13764,7 +13857,7 @@
               <c:f>模型一计算KDJ!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14088,6 +14181,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>192926.43862532912</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>288881.23881843378</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14109,11 +14205,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="389952256"/>
-        <c:axId val="389953792"/>
+        <c:axId val="483509376"/>
+        <c:axId val="483510912"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="389952256"/>
+        <c:axId val="483509376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14123,14 +14219,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="389953792"/>
+        <c:crossAx val="483510912"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="389953792"/>
+        <c:axId val="483510912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14141,7 +14237,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="389952256"/>
+        <c:crossAx val="483509376"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14183,7 +14279,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14221,7 +14317,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14262,7 +14358,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14300,7 +14396,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14343,7 +14439,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14381,7 +14477,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14659,7 +14755,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -14668,7 +14764,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB110"/>
+  <dimension ref="A1:AB111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -18564,6 +18660,35 @@
         <v>183014.52605583996</v>
       </c>
     </row>
+    <row r="111" spans="1:9" ht="12.75">
+      <c r="A111" s="13">
+        <v>46142</v>
+      </c>
+      <c r="B111" s="18">
+        <v>2.7899999618530273</v>
+      </c>
+      <c r="C111" s="14">
+        <v>2000</v>
+      </c>
+      <c r="D111" s="15">
+        <v>716.84588793745536</v>
+      </c>
+      <c r="E111" s="15">
+        <v>176726.7855023171</v>
+      </c>
+      <c r="F111" s="15">
+        <v>493067.72480987286</v>
+      </c>
+      <c r="G111" s="15">
+        <v>218000</v>
+      </c>
+      <c r="H111" s="15">
+        <v>493067.72480987286</v>
+      </c>
+      <c r="I111" s="15">
+        <v>275067.72480987286</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18575,7 +18700,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH110"/>
+  <dimension ref="A1:AH111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -18653,7 +18778,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -24156,6 +24281,50 @@
       </c>
       <c r="N110" s="21">
         <v>53.107937195450262</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" ht="12.75">
+      <c r="A111" s="13">
+        <v>46142</v>
+      </c>
+      <c r="B111" s="18">
+        <v>2.7899999618530273</v>
+      </c>
+      <c r="C111" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D111" s="15">
+        <v>716.84588793745536</v>
+      </c>
+      <c r="E111" s="15">
+        <v>184786.12636015928</v>
+      </c>
+      <c r="F111" s="15">
+        <v>515553.28549581306</v>
+      </c>
+      <c r="G111" s="15">
+        <v>225000</v>
+      </c>
+      <c r="H111" s="15">
+        <v>515553.28549581306</v>
+      </c>
+      <c r="I111" s="15">
+        <v>290553.28549581306</v>
+      </c>
+      <c r="J111" s="21">
+        <v>0.52300000190734863</v>
+      </c>
+      <c r="K111" s="21">
+        <v>0.1742169407075714</v>
+      </c>
+      <c r="L111" s="21">
+        <v>0.52300000190734863</v>
+      </c>
+      <c r="M111" s="23">
+        <v>0.2510786513695793</v>
+      </c>
+      <c r="N111" s="21">
+        <v>69.387397039635189</v>
       </c>
     </row>
   </sheetData>
@@ -24169,7 +24338,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AH110"/>
+  <dimension ref="A1:AH111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -24198,10 +24367,10 @@
   <sheetData>
     <row r="1" spans="1:34" s="1" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>2</v>
@@ -24225,28 +24394,28 @@
         <v>8</v>
       </c>
       <c r="J1" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="O1" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="P1" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="Q1" s="20" t="s">
         <v>29</v>
-      </c>
-      <c r="O1" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="P1" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q1" s="20" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1">
@@ -24256,7 +24425,7 @@
         <v>2000</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -30611,6 +30780,59 @@
         <v>64.583952119551526</v>
       </c>
     </row>
+    <row r="111" spans="1:17" ht="12.75">
+      <c r="A111" s="13">
+        <v>46142</v>
+      </c>
+      <c r="B111" s="18">
+        <v>2.7899999618530273</v>
+      </c>
+      <c r="C111" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D111" s="15">
+        <v>716.84588793745536</v>
+      </c>
+      <c r="E111" s="15">
+        <v>184186.82646759987</v>
+      </c>
+      <c r="F111" s="15">
+        <v>513881.23881843378</v>
+      </c>
+      <c r="G111" s="15">
+        <v>225000</v>
+      </c>
+      <c r="H111" s="15">
+        <v>513881.23881843378</v>
+      </c>
+      <c r="I111" s="15">
+        <v>288881.23881843378</v>
+      </c>
+      <c r="J111" s="15">
+        <v>2.8029999732971191</v>
+      </c>
+      <c r="K111" s="15">
+        <v>2.2599999904632568</v>
+      </c>
+      <c r="L111" s="19">
+        <v>2.8289999961853027</v>
+      </c>
+      <c r="M111" s="19">
+        <v>1.6579999923706055</v>
+      </c>
+      <c r="N111" s="21">
+        <v>96.669510315522857</v>
+      </c>
+      <c r="O111" s="21">
+        <v>78.933923614270611</v>
+      </c>
+      <c r="P111" s="21">
+        <v>74.84945409521751</v>
+      </c>
+      <c r="Q111" s="21">
+        <v>87.102862652376814</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/lai/valuationquan/AILOF/csiAILOFmodel1meancn.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel1meancn.xlsx
@@ -697,7 +697,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1024,6 +1024,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1033,7 +1036,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -1360,6 +1363,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>218000</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>220000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1402,7 +1408,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1729,6 +1735,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1738,7 +1747,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2065,6 +2074,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>493067.72480987286</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>542783.95352470258</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2107,7 +2119,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2434,6 +2446,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2443,7 +2458,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2770,6 +2785,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>275067.72480987286</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>322783.95352470258</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2791,11 +2809,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="514263296"/>
-        <c:axId val="525312768"/>
+        <c:axId val="459649408"/>
+        <c:axId val="459650944"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="514263296"/>
+        <c:axId val="459649408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2835,14 +2853,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="525312768"/>
+        <c:crossAx val="459650944"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="525312768"/>
+        <c:axId val="459650944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2891,7 +2909,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="514263296"/>
+        <c:crossAx val="459649408"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3021,7 +3039,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3348,6 +3366,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3357,7 +3378,7 @@
               <c:f>模型一!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3684,6 +3705,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>218000</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>220000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3717,7 +3741,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4044,6 +4068,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4053,7 +4080,7 @@
               <c:f>模型一!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4380,6 +4407,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>493067.72480987286</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>542783.95352470258</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4413,7 +4443,7 @@
               <c:f>模型一!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4740,6 +4770,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4749,7 +4782,7 @@
               <c:f>模型一!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5076,6 +5109,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>275067.72480987286</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>322783.95352470258</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5097,11 +5133,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="527323520"/>
-        <c:axId val="527325440"/>
+        <c:axId val="501033600"/>
+        <c:axId val="501068544"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="527323520"/>
+        <c:axId val="501033600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5111,14 +5147,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="527325440"/>
+        <c:crossAx val="501068544"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="527325440"/>
+        <c:axId val="501068544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5129,7 +5165,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="527323520"/>
+        <c:crossAx val="501033600"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5251,7 +5287,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5578,6 +5614,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5587,7 +5626,7 @@
               <c:f>模型一计算RSI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5914,6 +5953,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>225000</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>227000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5956,7 +5998,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6283,6 +6325,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6292,7 +6337,7 @@
               <c:f>模型一计算RSI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6619,6 +6664,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>515553.28549581306</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>567445.53608854045</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6661,7 +6709,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6988,6 +7036,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6997,7 +7048,7 @@
               <c:f>模型一计算RSI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7324,6 +7375,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>290553.28549581306</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>340445.53608854045</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7345,11 +7399,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="527359360"/>
-        <c:axId val="484852864"/>
+        <c:axId val="501081600"/>
+        <c:axId val="501083520"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="527359360"/>
+        <c:axId val="501081600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7389,14 +7443,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="484852864"/>
+        <c:crossAx val="501083520"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="484852864"/>
+        <c:axId val="501083520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7445,7 +7499,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="527359360"/>
+        <c:crossAx val="501081600"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7575,7 +7629,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7902,6 +7956,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7911,7 +7968,7 @@
               <c:f>模型一计算RSI!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8238,6 +8295,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>225000</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>227000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8271,7 +8331,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8598,6 +8658,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8607,7 +8670,7 @@
               <c:f>模型一计算RSI!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8934,6 +8997,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>515553.28549581306</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>567445.53608854045</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8967,7 +9033,7 @@
               <c:f>模型一计算RSI!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9294,6 +9360,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9303,7 +9372,7 @@
               <c:f>模型一计算RSI!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9630,6 +9699,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>290553.28549581306</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>340445.53608854045</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9651,11 +9723,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="484868096"/>
-        <c:axId val="484869632"/>
+        <c:axId val="614936960"/>
+        <c:axId val="614938880"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="484868096"/>
+        <c:axId val="614936960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9665,14 +9737,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="484869632"/>
+        <c:crossAx val="614938880"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="484869632"/>
+        <c:axId val="614938880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9683,7 +9755,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="484868096"/>
+        <c:crossAx val="614936960"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9805,7 +9877,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10132,6 +10204,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10141,7 +10216,7 @@
               <c:f>模型一计算KDJ!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -10468,6 +10543,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>225000</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>227000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10510,7 +10588,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10837,6 +10915,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10846,7 +10927,7 @@
               <c:f>模型一计算KDJ!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -11173,6 +11254,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>513881.23881843378</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>565611.67845160083</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11215,7 +11299,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11542,6 +11626,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11551,7 +11638,7 @@
               <c:f>模型一计算KDJ!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11878,6 +11965,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>288881.23881843378</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>338611.67845160083</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11899,11 +11989,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="483480320"/>
-        <c:axId val="483481856"/>
+        <c:axId val="497587712"/>
+        <c:axId val="497589248"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="483480320"/>
+        <c:axId val="497587712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11943,14 +12033,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="483481856"/>
+        <c:crossAx val="497589248"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="483481856"/>
+        <c:axId val="497589248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11999,7 +12089,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="483480320"/>
+        <c:crossAx val="497587712"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12129,7 +12219,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12456,6 +12546,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12465,7 +12558,7 @@
               <c:f>模型一计算KDJ!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -12792,6 +12885,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>225000</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>227000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12825,7 +12921,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13152,6 +13248,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13161,7 +13260,7 @@
               <c:f>模型一计算KDJ!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -13488,6 +13587,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>513881.23881843378</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>565611.67845160083</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13521,7 +13623,7 @@
               <c:f>模型一计算KDJ!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13848,6 +13950,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13857,7 +13962,7 @@
               <c:f>模型一计算KDJ!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14184,6 +14289,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>288881.23881843378</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>338611.67845160083</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14205,11 +14313,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="483509376"/>
-        <c:axId val="483510912"/>
+        <c:axId val="497624960"/>
+        <c:axId val="497626496"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="483509376"/>
+        <c:axId val="497624960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14219,14 +14327,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="483510912"/>
+        <c:crossAx val="497626496"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="483510912"/>
+        <c:axId val="497626496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14237,7 +14345,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="483509376"/>
+        <c:crossAx val="497624960"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14279,7 +14387,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14317,7 +14425,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14358,7 +14466,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14396,7 +14504,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14439,7 +14547,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14477,7 +14585,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14755,7 +14863,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -14764,7 +14872,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB111"/>
+  <dimension ref="A1:AB112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -18689,6 +18797,35 @@
         <v>275067.72480987286</v>
       </c>
     </row>
+    <row r="112" spans="1:9" ht="12.75">
+      <c r="A112" s="13">
+        <v>46171</v>
+      </c>
+      <c r="B112" s="18">
+        <v>3.059999942779541</v>
+      </c>
+      <c r="C112" s="14">
+        <v>2000</v>
+      </c>
+      <c r="D112" s="15">
+        <v>653.59478346372339</v>
+      </c>
+      <c r="E112" s="15">
+        <v>177380.38028578082</v>
+      </c>
+      <c r="F112" s="15">
+        <v>542783.95352470258</v>
+      </c>
+      <c r="G112" s="15">
+        <v>220000</v>
+      </c>
+      <c r="H112" s="15">
+        <v>542783.95352470258</v>
+      </c>
+      <c r="I112" s="15">
+        <v>322783.95352470258</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18700,7 +18837,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH111"/>
+  <dimension ref="A1:AH112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -24327,6 +24464,50 @@
         <v>69.387397039635189</v>
       </c>
     </row>
+    <row r="112" spans="1:14" ht="12.75">
+      <c r="A112" s="13">
+        <v>46171</v>
+      </c>
+      <c r="B112" s="18">
+        <v>3.059999942779541</v>
+      </c>
+      <c r="C112" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D112" s="15">
+        <v>653.59478346372339</v>
+      </c>
+      <c r="E112" s="15">
+        <v>185439.721143623</v>
+      </c>
+      <c r="F112" s="15">
+        <v>567445.53608854045</v>
+      </c>
+      <c r="G112" s="15">
+        <v>227000</v>
+      </c>
+      <c r="H112" s="15">
+        <v>567445.53608854045</v>
+      </c>
+      <c r="I112" s="15">
+        <v>340445.53608854045</v>
+      </c>
+      <c r="J112" s="21">
+        <v>0.26999998092651367</v>
+      </c>
+      <c r="K112" s="21">
+        <v>0.19018078074406178</v>
+      </c>
+      <c r="L112" s="21">
+        <v>0.26999998092651367</v>
+      </c>
+      <c r="M112" s="23">
+        <v>0.25423220629573501</v>
+      </c>
+      <c r="N112" s="21">
+        <v>74.805935689687729</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24338,7 +24519,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AH111"/>
+  <dimension ref="A1:AH112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -30833,6 +31014,59 @@
         <v>87.102862652376814</v>
       </c>
     </row>
+    <row r="112" spans="1:17" ht="12.75">
+      <c r="A112" s="13">
+        <v>46171</v>
+      </c>
+      <c r="B112" s="18">
+        <v>3.059999942779541</v>
+      </c>
+      <c r="C112" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D112" s="15">
+        <v>653.59478346372339</v>
+      </c>
+      <c r="E112" s="15">
+        <v>184840.42125106358</v>
+      </c>
+      <c r="F112" s="15">
+        <v>565611.67845160083</v>
+      </c>
+      <c r="G112" s="15">
+        <v>227000</v>
+      </c>
+      <c r="H112" s="15">
+        <v>565611.67845160083</v>
+      </c>
+      <c r="I112" s="15">
+        <v>338611.67845160083</v>
+      </c>
+      <c r="J112" s="15">
+        <v>3.2209999561309814</v>
+      </c>
+      <c r="K112" s="15">
+        <v>2.8250000476837158</v>
+      </c>
+      <c r="L112" s="19">
+        <v>3.2209999561309814</v>
+      </c>
+      <c r="M112" s="19">
+        <v>2.0439999103546143</v>
+      </c>
+      <c r="N112" s="21">
+        <v>86.321154877675269</v>
+      </c>
+      <c r="O112" s="21">
+        <v>81.396334035405502</v>
+      </c>
+      <c r="P112" s="21">
+        <v>77.031747408613512</v>
+      </c>
+      <c r="Q112" s="21">
+        <v>90.125507288989468</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
